--- a/input/timetable/История-.xlsx
+++ b/input/timetable/История-.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28740" windowHeight="13890" tabRatio="603" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28740" windowHeight="13890" tabRatio="603" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="1 курс" sheetId="25" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="161">
   <si>
     <t>пара</t>
   </si>
@@ -77,6 +77,9 @@
     <t>Зав. кафедрой</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -125,27 +128,78 @@
     <t>Русский язык и культура речи (лек 32 ч)</t>
   </si>
   <si>
+    <t>Хадынская А.А.</t>
+  </si>
+  <si>
+    <t>Зибаев А.В.</t>
+  </si>
+  <si>
+    <t>Визгалов Г.П.</t>
+  </si>
+  <si>
+    <t>Лешукова Е.В.</t>
+  </si>
+  <si>
+    <t>Веселов С.И.</t>
+  </si>
+  <si>
     <t>Работа в команде (лек 32 ч)</t>
   </si>
   <si>
+    <t>Кузнецова А.А.</t>
+  </si>
+  <si>
+    <t>Кайдалова А.А.</t>
+  </si>
+  <si>
+    <t>Задорожняя О.А.</t>
+  </si>
+  <si>
     <t>История отечественной культуры (лек), Г107</t>
   </si>
   <si>
     <t>История отечественной культуры (пр), Г107</t>
   </si>
   <si>
+    <t>Кирилюк Д.В.</t>
+  </si>
+  <si>
+    <t>Сердюков Д.В.</t>
+  </si>
+  <si>
     <t>204-31</t>
   </si>
   <si>
+    <t>Кардаш О.В.</t>
+  </si>
+  <si>
+    <t>Задорожняя О.А., Зибаев А.В.</t>
+  </si>
+  <si>
     <t>Основы проектной деятельности (лекция 16 ч)</t>
   </si>
   <si>
     <t>204-21</t>
   </si>
   <si>
+    <t>Менбариева Е.Г.</t>
+  </si>
+  <si>
     <t>Психология инклюзивного общества (лекция16 ч)</t>
   </si>
   <si>
+    <t>Меренков В.А.</t>
+  </si>
+  <si>
+    <t>Ткаченко Т.С.</t>
+  </si>
+  <si>
+    <t>Селянина М.Ю.</t>
+  </si>
+  <si>
+    <t>Исаева Т.А.</t>
+  </si>
+  <si>
     <t>Отечественная история (до XX в.) (лек), Г108</t>
   </si>
   <si>
@@ -197,15 +251,30 @@
     <t>204-41</t>
   </si>
   <si>
+    <t>Лепихина Ю.В.</t>
+  </si>
+  <si>
     <t>Цифровая грамотность (лек 16 ч)</t>
   </si>
   <si>
+    <t>Мойсеенкова М.А.</t>
+  </si>
+  <si>
+    <t>Мойсеенкова М.А</t>
+  </si>
+  <si>
     <t>ФТД: Ссылка и каторга в российской политической истории (лек)/(пр), Г107</t>
   </si>
   <si>
     <t>Философия (лек 32 ч)</t>
   </si>
   <si>
+    <t>Кулагина И.В.</t>
+  </si>
+  <si>
+    <t>Осипова А.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Примечание: *  </t>
   </si>
   <si>
@@ -218,18 +287,27 @@
     <t>Основы научно-исследовательской деятельности (лек)/(пр), Г107</t>
   </si>
   <si>
+    <t>Веселов С.И./Сташкин П.Р.</t>
+  </si>
+  <si>
     <t>ДВ 02.02: Основы музеефикации объектов культурного и природного наследия (лек)/(пр), Г108</t>
   </si>
   <si>
     <t>ДВ 02.02: Основы музеефикации объектов культурного и природного наследия (пр), Г108//</t>
   </si>
   <si>
+    <t>Белоус П.В.</t>
+  </si>
+  <si>
     <t>История отечественной исторической науки (пр), Г225</t>
   </si>
   <si>
     <t>ДВ 07.01:Культура коренных народов Севера (лек),/(пр) Г225</t>
   </si>
   <si>
+    <t>Галлямова Л.В.</t>
+  </si>
+  <si>
     <t>История Сибири (XX-нач.XXI вв.)(пр), Г106</t>
   </si>
   <si>
@@ -266,6 +344,9 @@
     <t>Цифровая грамотность (пр), К433</t>
   </si>
   <si>
+    <t>Бастинович Е.В.</t>
+  </si>
+  <si>
     <t>Охрана культурного и природного наследия в России и за рубежом (пр), Г107</t>
   </si>
   <si>
@@ -281,6 +362,12 @@
     <t>Элективные дисциплины по физической культуре и спорту проводятся  1 парой или  2 парой в зависимости от выбранной элективной дисциплины</t>
   </si>
   <si>
+    <t>Осипова А.В./Калинина Е.А.</t>
+  </si>
+  <si>
+    <t>Афян К.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык, п/г 2, К413</t>
   </si>
   <si>
@@ -293,6 +380,9 @@
     <t>Новая и новейшая история стран Европы и Америки (пр), Г225</t>
   </si>
   <si>
+    <t>Магарамов А.А.</t>
+  </si>
+  <si>
     <t>Отечественная история (XX в.) (пр), Г225</t>
   </si>
   <si>
@@ -305,12 +395,18 @@
     <t>Б1.О.ДВ 03.02: Геополитика в истории международных отношений (лек)/(пр), Г225</t>
   </si>
   <si>
+    <t>Задорожняя О.А.; Лешукова Е.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Б1.О.ДВ 03.02: Геополитика в истории международных отношений (пр), Г225// </t>
   </si>
   <si>
     <t>Новая и новейшая история стран Европы и Америки (лек), Г225// Психология инклюзивного общества (пр), Г225</t>
   </si>
   <si>
+    <t>Кузнецова А.А./Меренков В.А.</t>
+  </si>
+  <si>
     <t>Иностранный язык в проф. сфере (24 ч), п/г 1, К406</t>
   </si>
   <si>
@@ -326,6 +422,9 @@
     <t>Музееведение (лек)/(пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Задорожняя О.А.; Овчинникова Н.В.</t>
+  </si>
+  <si>
     <t>История науки и техники (лек). Г108</t>
   </si>
   <si>
@@ -366,6 +465,12 @@
   </si>
   <si>
     <t>//Иностранный язык в проф. сфере, п/г 2, К408</t>
+  </si>
+  <si>
+    <t>; Афян К.А.</t>
+  </si>
+  <si>
+    <t>Воробьева А.Д.</t>
   </si>
   <si>
     <t>Иностранный язык, п/г 1, Г104</t>
@@ -510,7 +615,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,12 +634,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="61">
     <border>
       <left/>
       <right/>
@@ -651,6 +762,19 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -795,6 +919,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="medium">
@@ -1112,6 +1249,19 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1161,6 +1311,32 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1243,7 +1419,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1283,24 +1459,27 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1329,85 +1508,92 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1415,319 +1601,337 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2038,7 +2242,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2047,10 +2251,11 @@
     <col min="4" max="4" width="19.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2058,15 +2263,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2074,13 +2279,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2090,27 +2295,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>19</v>
+      <c r="C7" s="80" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -2120,35 +2325,35 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="82" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-    </row>
-    <row r="10" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+    </row>
+    <row r="10" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>0</v>
@@ -2159,345 +2364,422 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-    </row>
-    <row r="11" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="115" t="s">
+      <c r="C11" s="124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="126"/>
+      <c r="G11" s="94" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="128"/>
+      <c r="E12" s="128"/>
+      <c r="F12" s="129"/>
+      <c r="G12" s="93" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="105"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="93"/>
+    </row>
+    <row r="14" spans="1:16" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
+        <v>5</v>
+      </c>
+      <c r="C14" s="121"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="93"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1</v>
+      </c>
+      <c r="C15" s="118" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="99" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="62"/>
+    </row>
+    <row r="16" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="104"/>
+      <c r="G16" s="91" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="102" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="91" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
+        <v>4</v>
+      </c>
+      <c r="C18" s="130" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="132"/>
+      <c r="G18" s="91" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="25">
+        <v>1</v>
+      </c>
+      <c r="C19" s="111"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="94"/>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>2</v>
+      </c>
+      <c r="C20" s="105"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="107"/>
+      <c r="G20" s="85" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>3</v>
+      </c>
+      <c r="C21" s="105" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="85" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>4</v>
+      </c>
+      <c r="C22" s="102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="104"/>
+      <c r="G22" s="87" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="30"/>
+      <c r="B23" s="29">
+        <v>5</v>
+      </c>
+      <c r="C23" s="114"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="115"/>
+      <c r="F23" s="116"/>
+      <c r="G23" s="84"/>
+    </row>
+    <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="25">
+        <v>2</v>
+      </c>
+      <c r="C24" s="108" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="109"/>
+      <c r="E24" s="109"/>
+      <c r="F24" s="110"/>
+      <c r="G24" s="87" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>3</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="87" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
+        <v>4</v>
+      </c>
+      <c r="C26" s="105" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
+      <c r="G26" s="93" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="30"/>
+      <c r="B27" s="29">
+        <v>5</v>
+      </c>
+      <c r="C27" s="148"/>
+      <c r="D27" s="149"/>
+      <c r="E27" s="134" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" s="135"/>
+      <c r="G27" s="95" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="25">
+        <v>2</v>
+      </c>
+      <c r="C28" s="150" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="152"/>
+      <c r="G28" s="86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="127" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="128"/>
+      <c r="E29" s="128"/>
+      <c r="F29" s="129"/>
+      <c r="G29" s="89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="31"/>
+      <c r="B30" s="27">
+        <v>4</v>
+      </c>
+      <c r="C30" s="105" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="93" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="32"/>
+      <c r="B31" s="29">
+        <v>5</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="93" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="25">
+        <v>2</v>
+      </c>
+      <c r="C32" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" s="143"/>
+      <c r="E32" s="143"/>
+      <c r="F32" s="144"/>
+      <c r="G32" s="92" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="35"/>
+      <c r="B33" s="36">
+        <v>4</v>
+      </c>
+      <c r="C33" s="127" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="128"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="129"/>
+      <c r="G33" s="89" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="38"/>
+      <c r="B34" s="29">
+        <v>5</v>
+      </c>
+      <c r="C34" s="136" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="138"/>
+      <c r="G34" s="89" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A36" s="45"/>
+      <c r="B36" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="139" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="140"/>
+      <c r="E36" s="140"/>
+      <c r="F36" s="141"/>
+      <c r="G36" s="86" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="47"/>
+      <c r="B37" s="67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="145" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="146"/>
+      <c r="E37" s="146"/>
+      <c r="F37" s="147"/>
+      <c r="G37" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="117"/>
-    </row>
-    <row r="12" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
-        <v>3</v>
-      </c>
-      <c r="C12" s="91" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="93"/>
-    </row>
-    <row r="13" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>4</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="81"/>
-    </row>
-    <row r="14" spans="1:15" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
-        <v>5</v>
-      </c>
-      <c r="C14" s="112"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="24">
-        <v>1</v>
-      </c>
-      <c r="C15" s="109" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="111"/>
-      <c r="O15" s="59"/>
-    </row>
-    <row r="16" spans="1:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>2</v>
-      </c>
-      <c r="C16" s="97" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="99"/>
-    </row>
-    <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="97" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="98"/>
-      <c r="E17" s="98"/>
-      <c r="F17" s="99"/>
-    </row>
-    <row r="18" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
-        <v>4</v>
-      </c>
-      <c r="C18" s="76" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="78"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="24">
-        <v>1</v>
-      </c>
-      <c r="C19" s="121"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="122"/>
-      <c r="F19" s="123"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>2</v>
-      </c>
-      <c r="C20" s="79"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="79" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="80"/>
-      <c r="E21" s="80"/>
-      <c r="F21" s="81"/>
-    </row>
-    <row r="22" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>4</v>
-      </c>
-      <c r="C22" s="97" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="99"/>
-    </row>
-    <row r="23" spans="1:6" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="29"/>
-      <c r="B23" s="28">
-        <v>5</v>
-      </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="125"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="126"/>
-    </row>
-    <row r="24" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="24">
-        <v>2</v>
-      </c>
-      <c r="C24" s="118" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-    </row>
-    <row r="25" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>3</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
-        <v>4</v>
-      </c>
-      <c r="C26" s="79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26" s="80"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-    </row>
-    <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="29"/>
-      <c r="B27" s="28">
-        <v>5</v>
-      </c>
-      <c r="C27" s="103"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="84"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="24">
-        <v>2</v>
-      </c>
-      <c r="C28" s="105" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="106"/>
-      <c r="E28" s="106"/>
-      <c r="F28" s="107"/>
-    </row>
-    <row r="29" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="91" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="92"/>
-      <c r="E29" s="92"/>
-      <c r="F29" s="93"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="26">
-        <v>4</v>
-      </c>
-      <c r="C30" s="79" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81"/>
-    </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="31"/>
-      <c r="B31" s="28">
-        <v>5</v>
-      </c>
-      <c r="C31" s="97" t="s">
-        <v>42</v>
-      </c>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="99"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="24">
-        <v>2</v>
-      </c>
-      <c r="C32" s="94" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32" s="95"/>
-      <c r="E32" s="95"/>
-      <c r="F32" s="96"/>
-    </row>
-    <row r="33" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="33"/>
-      <c r="B33" s="34">
-        <v>4</v>
-      </c>
-      <c r="C33" s="91" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="93"/>
-    </row>
-    <row r="34" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="28">
-        <v>5</v>
-      </c>
-      <c r="C34" s="85" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="86"/>
-      <c r="E34" s="86"/>
-      <c r="F34" s="87"/>
-    </row>
-    <row r="35" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="41"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A36" s="42"/>
-      <c r="B36" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="88" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="89"/>
-      <c r="E36" s="89"/>
-      <c r="F36" s="90"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="44"/>
-      <c r="B37" s="63" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="100" t="s">
-        <v>58</v>
-      </c>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="102"/>
-    </row>
-    <row r="38" spans="1:6" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="45"/>
-      <c r="B38" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="82" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="84"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="48"/>
+      <c r="B38" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="133" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="84" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -2505,7 +2787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B40" s="2" t="s">
         <v>17</v>
       </c>
@@ -2515,21 +2797,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="C26:F26"/>
@@ -2546,6 +2813,21 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="C28:F28"/>
     <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C23:F23"/>
   </mergeCells>
   <conditionalFormatting sqref="C9">
     <cfRule type="expression" priority="1">
@@ -2568,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -2577,10 +2859,11 @@
     <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.28515625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -2588,15 +2871,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2604,13 +2887,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -2620,29 +2903,29 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="72"/>
+      <c r="C7" s="80" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="80"/>
       <c r="E7" s="10">
         <v>2</v>
       </c>
@@ -2650,37 +2933,37 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="47" t="s">
+    <row r="9" spans="1:9" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="19" t="s">
@@ -2689,365 +2972,437 @@
       <c r="D10" s="20"/>
       <c r="E10" s="21"/>
       <c r="F10" s="22"/>
-      <c r="H10" s="52"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="145" t="s">
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="55"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A11" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="162" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="163"/>
+      <c r="E11" s="163"/>
+      <c r="F11" s="164"/>
+      <c r="G11" s="83"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>4</v>
+      </c>
+      <c r="C12" s="105" t="s">
+        <v>116</v>
+      </c>
+      <c r="D12" s="106"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="87" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="68"/>
+      <c r="B13" s="58">
+        <v>5</v>
+      </c>
+      <c r="C13" s="105" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="106"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="28"/>
+      <c r="B14" s="29">
+        <v>6</v>
+      </c>
+      <c r="C14" s="153"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="170" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="171"/>
+      <c r="G14" s="84" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1</v>
+      </c>
+      <c r="C15" s="165"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="166"/>
+      <c r="F15" s="167"/>
+      <c r="G15" s="34"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>2</v>
+      </c>
+      <c r="C16" s="127" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="128"/>
+      <c r="E16" s="128"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>3</v>
+      </c>
+      <c r="C17" s="127" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="26"/>
+      <c r="B18" s="27">
+        <v>4</v>
+      </c>
+      <c r="C18" s="105" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="106"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="87" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="25">
+        <v>2</v>
+      </c>
+      <c r="C19" s="156" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="157"/>
+      <c r="E19" s="157"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="86" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>3</v>
+      </c>
+      <c r="C20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>4</v>
+      </c>
+      <c r="C21" s="159"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="87"/>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="29">
+        <v>5</v>
+      </c>
+      <c r="C22" s="114"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="84"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="162" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="163"/>
+      <c r="E23" s="163"/>
+      <c r="F23" s="164"/>
+      <c r="G23" s="79"/>
+    </row>
+    <row r="24" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>4</v>
+      </c>
+      <c r="C24" s="105" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="106"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="68"/>
+      <c r="B25" s="58">
+        <v>5</v>
+      </c>
+      <c r="C25" s="105" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29">
+        <v>6</v>
+      </c>
+      <c r="C26" s="153"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="155"/>
+      <c r="G26" s="77"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="25">
+        <v>1</v>
+      </c>
+      <c r="C27" s="173"/>
+      <c r="D27" s="174"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="175"/>
+      <c r="G27" s="34"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="27">
+        <v>2</v>
+      </c>
+      <c r="C28" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="27">
+        <v>3</v>
+      </c>
+      <c r="C29" s="176" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="177"/>
+      <c r="E29" s="177"/>
+      <c r="F29" s="178"/>
+      <c r="G29" s="89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A30" s="57"/>
+      <c r="B30" s="58">
+        <v>4</v>
+      </c>
+      <c r="C30" s="127" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="128"/>
+      <c r="E30" s="128"/>
+      <c r="F30" s="129"/>
+      <c r="G30" s="89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="32"/>
+      <c r="B31" s="29">
+        <v>5</v>
+      </c>
+      <c r="C31" s="179"/>
+      <c r="D31" s="180"/>
+      <c r="E31" s="180"/>
+      <c r="F31" s="181"/>
+      <c r="G31" s="39"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="25">
+        <v>1</v>
+      </c>
+      <c r="C32" s="156" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
-      <c r="F11" s="147"/>
-    </row>
-    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="92" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27">
+        <v>2</v>
+      </c>
+      <c r="C33" s="127" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="128"/>
+      <c r="E33" s="128"/>
+      <c r="F33" s="129"/>
+      <c r="G33" s="89" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="63"/>
+      <c r="B34" s="58">
+        <v>3</v>
+      </c>
+      <c r="C34" s="127" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="128"/>
+      <c r="E34" s="128"/>
+      <c r="F34" s="129"/>
+      <c r="G34" s="89" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="38"/>
+      <c r="B35" s="29">
         <v>4</v>
       </c>
-      <c r="C12" s="79" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="149"/>
-    </row>
-    <row r="13" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="64"/>
-      <c r="B13" s="55">
-        <v>5</v>
-      </c>
-      <c r="C13" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="81"/>
-    </row>
-    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28">
-        <v>6</v>
-      </c>
-      <c r="C14" s="150"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="152" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="153"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="24">
-        <v>1</v>
-      </c>
-      <c r="C15" s="142"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="144"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>2</v>
-      </c>
-      <c r="C16" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="92"/>
-      <c r="E16" s="92"/>
-      <c r="F16" s="93"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="92"/>
-      <c r="E17" s="92"/>
-      <c r="F17" s="93"/>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26">
-        <v>4</v>
-      </c>
-      <c r="C18" s="79" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="81"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="24">
-        <v>2</v>
-      </c>
-      <c r="C19" s="137" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="138"/>
-      <c r="E19" s="138"/>
-      <c r="F19" s="139"/>
-    </row>
-    <row r="20" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>3</v>
-      </c>
-      <c r="C20" s="79" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>4</v>
-      </c>
-      <c r="C21" s="155"/>
-      <c r="D21" s="156"/>
-      <c r="E21" s="156"/>
-      <c r="F21" s="157"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>5</v>
-      </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="125"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="126"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="145" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="146"/>
-      <c r="E23" s="146"/>
-      <c r="F23" s="147"/>
-    </row>
-    <row r="24" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>4</v>
-      </c>
-      <c r="C24" s="79" t="s">
-        <v>121</v>
-      </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="80"/>
-      <c r="F24" s="81"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="64"/>
-      <c r="B25" s="55">
-        <v>5</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="81"/>
-    </row>
-    <row r="26" spans="1:6" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28">
-        <v>6</v>
-      </c>
-      <c r="C26" s="150"/>
-      <c r="D26" s="151"/>
-      <c r="E26" s="151"/>
-      <c r="F26" s="154"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="24">
-        <v>1</v>
-      </c>
-      <c r="C27" s="128"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="130"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26">
-        <v>2</v>
-      </c>
-      <c r="C28" s="91" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="93"/>
-    </row>
-    <row r="29" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>3</v>
-      </c>
-      <c r="C29" s="131" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="133"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A30" s="54"/>
-      <c r="B30" s="55">
-        <v>4</v>
-      </c>
-      <c r="C30" s="91" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="92"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="93"/>
-    </row>
-    <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="31"/>
-      <c r="B31" s="28">
-        <v>5</v>
-      </c>
-      <c r="C31" s="134"/>
-      <c r="D31" s="135"/>
-      <c r="E31" s="135"/>
-      <c r="F31" s="136"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="24">
-        <v>1</v>
-      </c>
-      <c r="C32" s="137" t="s">
-        <v>52</v>
-      </c>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="139"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="35"/>
-      <c r="B33" s="26">
-        <v>2</v>
-      </c>
-      <c r="C33" s="91" t="s">
+      <c r="C35" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="89" t="s">
         <v>53</v>
       </c>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="93"/>
-    </row>
-    <row r="34" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="60"/>
-      <c r="B34" s="55">
-        <v>3</v>
-      </c>
-      <c r="C34" s="91" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="92"/>
-      <c r="E34" s="92"/>
-      <c r="F34" s="93"/>
-    </row>
-    <row r="35" spans="1:6" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="36"/>
-      <c r="B35" s="28">
-        <v>4</v>
-      </c>
-      <c r="C35" s="85" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="86"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="87"/>
-    </row>
-    <row r="36" spans="1:6" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="58"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A37" s="65"/>
-      <c r="B37" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="138" t="s">
-        <v>38</v>
-      </c>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A38" s="66"/>
-      <c r="B38" s="68" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38" s="101" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="101"/>
-      <c r="E38" s="101"/>
-      <c r="F38" s="101"/>
-    </row>
-    <row r="39" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="75"/>
-      <c r="B39" s="69" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="140" t="s">
-        <v>60</v>
-      </c>
-      <c r="D39" s="141"/>
-      <c r="E39" s="141"/>
-      <c r="F39" s="141"/>
-    </row>
-    <row r="40" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="127"/>
-      <c r="E40" s="127"/>
-      <c r="F40" s="127"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:7" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="40"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A37" s="69"/>
+      <c r="B37" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="157" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="157"/>
+      <c r="E37" s="157"/>
+      <c r="F37" s="157"/>
+      <c r="G37" s="92" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A38" s="70"/>
+      <c r="B38" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="146"/>
+      <c r="E38" s="146"/>
+      <c r="F38" s="146"/>
+      <c r="G38" s="89" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="97"/>
+      <c r="B39" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="182" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="183"/>
+      <c r="E39" s="183"/>
+      <c r="F39" s="183"/>
+      <c r="G39" s="98" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="76"/>
+      <c r="C40" s="172" t="s">
+        <v>112</v>
+      </c>
+      <c r="D40" s="172"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="172"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
@@ -3055,7 +3410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B42" s="2" t="s">
         <v>17</v>
       </c>
@@ -3065,25 +3420,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C34:F34"/>
     <mergeCell ref="C27:F27"/>
@@ -3097,6 +3433,25 @@
     <mergeCell ref="C35:F35"/>
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="C39:F39"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C25:F25"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
@@ -3127,7 +3482,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3136,10 +3491,11 @@
     <col min="4" max="4" width="22" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3147,15 +3503,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3163,13 +3519,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3179,27 +3535,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>19</v>
+      <c r="C7" s="80" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -3209,375 +3565,446 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="73" t="s">
+    <row r="9" spans="1:7" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="36">
+        <v>2</v>
+      </c>
+      <c r="C11" s="184" t="s">
+        <v>154</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="92" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="176" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="177"/>
+      <c r="E12" s="177"/>
+      <c r="F12" s="178"/>
+      <c r="G12" s="89" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="176" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="177"/>
+      <c r="E13" s="177"/>
+      <c r="F13" s="178"/>
+      <c r="G13" s="89" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="26"/>
+      <c r="B14" s="27">
+        <v>5</v>
+      </c>
+      <c r="C14" s="176" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="177"/>
+      <c r="E14" s="177"/>
+      <c r="F14" s="178"/>
+      <c r="G14" s="89" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="25">
+        <v>2</v>
+      </c>
+      <c r="C15" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="92" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="193" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
+      <c r="F16" s="195"/>
+      <c r="G16" s="89" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="193" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="89" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" s="68"/>
+      <c r="B18" s="58">
+        <v>5</v>
+      </c>
+      <c r="C18" s="145" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="146"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="100" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="30"/>
+      <c r="B19" s="29">
+        <v>7</v>
+      </c>
+      <c r="C19" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="196"/>
+      <c r="G19" s="98" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="25">
+        <v>2</v>
+      </c>
+      <c r="C20" s="156" t="s">
+        <v>121</v>
+      </c>
+      <c r="D20" s="157"/>
+      <c r="E20" s="157"/>
+      <c r="F20" s="158"/>
+      <c r="G20" s="92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>3</v>
+      </c>
+      <c r="C21" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="128"/>
+      <c r="E21" s="128"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="89" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27">
+        <v>4</v>
+      </c>
+      <c r="C22" s="127" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="128"/>
+      <c r="E22" s="128"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27">
+        <v>5</v>
+      </c>
+      <c r="C23" s="197" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="198"/>
+      <c r="E23" s="198"/>
+      <c r="F23" s="199"/>
+      <c r="G23" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="30"/>
+      <c r="B24" s="29">
+        <v>7</v>
+      </c>
+      <c r="C24" s="182" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" s="183"/>
+      <c r="E24" s="183"/>
+      <c r="F24" s="196"/>
+      <c r="G24" s="98" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="25">
+        <v>1</v>
+      </c>
+      <c r="C25" s="127" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="129"/>
+      <c r="G25" s="89" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="26"/>
+      <c r="B26" s="27">
+        <v>3</v>
+      </c>
+      <c r="C26" s="127" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="129"/>
+      <c r="G26" s="89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="26"/>
+      <c r="B27" s="27">
+        <v>4</v>
+      </c>
+      <c r="C27" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="89" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="30"/>
+      <c r="B28" s="29">
+        <v>5</v>
+      </c>
+      <c r="C28" s="187" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="188"/>
+      <c r="E28" s="188"/>
+      <c r="F28" s="189"/>
+      <c r="G28" s="98" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="190" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="191"/>
+      <c r="E29" s="191"/>
+      <c r="F29" s="192"/>
+      <c r="G29" s="78"/>
+    </row>
+    <row r="30" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="31"/>
+      <c r="B30" s="27">
+        <v>5</v>
+      </c>
+      <c r="C30" s="105" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="107"/>
+      <c r="G30" s="85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="32"/>
+      <c r="B31" s="29">
+        <v>6</v>
+      </c>
+      <c r="C31" s="204"/>
+      <c r="D31" s="205"/>
+      <c r="E31" s="206" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="207"/>
+      <c r="G31" s="85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A32" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="108" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="48" t="s">
+      <c r="B32" s="25">
         <v>1</v>
       </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
-    </row>
-    <row r="11" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="C32" s="156" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="157"/>
+      <c r="E32" s="157"/>
+      <c r="F32" s="158"/>
+      <c r="G32" s="92"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A33" s="31"/>
+      <c r="B33" s="27">
         <v>2</v>
       </c>
-      <c r="C11" s="179" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" s="180"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="181"/>
-    </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C33" s="145"/>
+      <c r="D33" s="146"/>
+      <c r="E33" s="146"/>
+      <c r="F33" s="147"/>
+      <c r="G33" s="100"/>
+    </row>
+    <row r="34" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="32"/>
+      <c r="B34" s="29">
         <v>3</v>
       </c>
-      <c r="C12" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="133"/>
-    </row>
-    <row r="13" spans="1:6" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
-        <v>4</v>
-      </c>
-      <c r="C13" s="131" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="133"/>
-    </row>
-    <row r="14" spans="1:6" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26">
-        <v>5</v>
-      </c>
-      <c r="C14" s="131" t="s">
-        <v>125</v>
-      </c>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="133"/>
-    </row>
-    <row r="15" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="24">
-        <v>2</v>
-      </c>
-      <c r="C15" s="115" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>3</v>
-      </c>
-      <c r="C16" s="172" t="s">
-        <v>89</v>
-      </c>
-      <c r="D16" s="173"/>
-      <c r="E16" s="173"/>
-      <c r="F16" s="174"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>4</v>
-      </c>
-      <c r="C17" s="172" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" s="173"/>
-      <c r="E17" s="173"/>
-      <c r="F17" s="174"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="64"/>
-      <c r="B18" s="55">
-        <v>5</v>
-      </c>
-      <c r="C18" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="102"/>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="29"/>
-      <c r="B19" s="28">
-        <v>7</v>
-      </c>
-      <c r="C19" s="140" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="175"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="24">
-        <v>2</v>
-      </c>
-      <c r="C20" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="139"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>3</v>
-      </c>
-      <c r="C21" s="91" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="93"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="25"/>
-      <c r="B22" s="26">
-        <v>4</v>
-      </c>
-      <c r="C22" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="92"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="93"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="25"/>
-      <c r="B23" s="26">
-        <v>5</v>
-      </c>
-      <c r="C23" s="176" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="177"/>
-      <c r="E23" s="177"/>
-      <c r="F23" s="178"/>
-    </row>
-    <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="29"/>
-      <c r="B24" s="28">
-        <v>7</v>
-      </c>
-      <c r="C24" s="140" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="141"/>
-      <c r="E24" s="141"/>
-      <c r="F24" s="175"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="24">
-        <v>1</v>
-      </c>
-      <c r="C25" s="91" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="93"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="26">
-        <v>3</v>
-      </c>
-      <c r="C26" s="91" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="92"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="93"/>
-    </row>
-    <row r="27" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="25"/>
-      <c r="B27" s="26">
-        <v>4</v>
-      </c>
-      <c r="C27" s="91" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="93"/>
-    </row>
-    <row r="28" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="29"/>
-      <c r="B28" s="28">
-        <v>5</v>
-      </c>
-      <c r="C28" s="182" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="183"/>
-      <c r="E28" s="183"/>
-      <c r="F28" s="184"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="185" t="s">
-        <v>71</v>
-      </c>
-      <c r="D29" s="186"/>
-      <c r="E29" s="186"/>
-      <c r="F29" s="187"/>
-    </row>
-    <row r="30" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="26">
-        <v>5</v>
-      </c>
-      <c r="C30" s="79" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81"/>
-    </row>
-    <row r="31" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="31"/>
-      <c r="B31" s="28">
-        <v>6</v>
-      </c>
-      <c r="C31" s="162"/>
-      <c r="D31" s="163"/>
-      <c r="E31" s="164" t="s">
-        <v>97</v>
-      </c>
-      <c r="F31" s="165"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="24">
-        <v>1</v>
-      </c>
-      <c r="C32" s="137" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="139"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A33" s="30"/>
-      <c r="B33" s="26">
-        <v>2</v>
-      </c>
-      <c r="C33" s="100"/>
-      <c r="D33" s="101"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="31"/>
-      <c r="B34" s="28">
-        <v>3</v>
-      </c>
-      <c r="C34" s="158"/>
-      <c r="D34" s="159"/>
-      <c r="E34" s="159"/>
-      <c r="F34" s="160"/>
-    </row>
-    <row r="35" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="166"/>
-      <c r="D35" s="167"/>
-      <c r="E35" s="167"/>
-      <c r="F35" s="168"/>
-    </row>
-    <row r="36" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="61"/>
-      <c r="B36" s="62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C36" s="169" t="s">
-        <v>40</v>
-      </c>
-      <c r="D36" s="170"/>
-      <c r="E36" s="170"/>
-      <c r="F36" s="171"/>
-    </row>
-    <row r="37" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="71"/>
-      <c r="C37" s="161" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="161"/>
-      <c r="E37" s="161"/>
-      <c r="F37" s="161"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="200"/>
+      <c r="D34" s="201"/>
+      <c r="E34" s="201"/>
+      <c r="F34" s="202"/>
+      <c r="G34" s="89"/>
+    </row>
+    <row r="35" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="40"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="208"/>
+      <c r="D35" s="209"/>
+      <c r="E35" s="209"/>
+      <c r="F35" s="210"/>
+      <c r="G35" s="66"/>
+    </row>
+    <row r="36" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="64"/>
+      <c r="B36" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="211" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="212"/>
+      <c r="E36" s="212"/>
+      <c r="F36" s="213"/>
+      <c r="G36" s="90" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="76"/>
+      <c r="C37" s="203" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="203"/>
+      <c r="E37" s="203"/>
+      <c r="F37" s="203"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
@@ -3585,7 +4012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B39" s="2" t="s">
         <v>17</v>
       </c>
@@ -3595,10 +4022,16 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="C32:F32"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="C27:F27"/>
     <mergeCell ref="C16:F16"/>
@@ -3615,16 +4048,10 @@
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C37:F37"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C18:F18"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6">
@@ -3655,7 +4082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -3664,10 +4091,11 @@
     <col min="4" max="4" width="19" style="2" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="20" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -3675,15 +4103,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -3691,13 +4119,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="F4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -3707,27 +4135,27 @@
       <c r="E5" s="5"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="72" t="s">
-        <v>19</v>
+      <c r="C7" s="80" t="s">
+        <v>20</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="10">
@@ -3737,352 +4165,427 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="82" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="73" t="s">
+    <row r="9" spans="1:7" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="117" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="36">
+        <v>2</v>
+      </c>
+      <c r="C11" s="214" t="s">
+        <v>134</v>
+      </c>
+      <c r="D11" s="185"/>
+      <c r="E11" s="185"/>
+      <c r="F11" s="186"/>
+      <c r="G11" s="92" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="26"/>
+      <c r="B12" s="27">
+        <v>3</v>
+      </c>
+      <c r="C12" s="215" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="217"/>
+      <c r="G12" s="89" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27">
+        <v>4</v>
+      </c>
+      <c r="C13" s="176" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="177"/>
+      <c r="E13" s="177"/>
+      <c r="F13" s="178"/>
+      <c r="G13" s="89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="68"/>
+      <c r="B14" s="58">
+        <v>5</v>
+      </c>
+      <c r="C14" s="218" t="s">
+        <v>137</v>
+      </c>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+      <c r="F14" s="220"/>
+      <c r="G14" s="101" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="25">
+        <v>2</v>
+      </c>
+      <c r="C15" s="124" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="125"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="126"/>
+      <c r="G15" s="92" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="176" t="s">
+        <v>152</v>
+      </c>
+      <c r="D16" s="177"/>
+      <c r="E16" s="177"/>
+      <c r="F16" s="178"/>
+      <c r="G16" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27">
+        <v>4</v>
+      </c>
+      <c r="C17" s="176" t="s">
+        <v>138</v>
+      </c>
+      <c r="D17" s="177"/>
+      <c r="E17" s="177"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="30"/>
+      <c r="B18" s="29">
+        <v>5</v>
+      </c>
+      <c r="C18" s="136" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="98" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="25">
+        <v>2</v>
+      </c>
+      <c r="C19" s="224" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="86" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="26"/>
+      <c r="B20" s="27">
+        <v>3</v>
+      </c>
+      <c r="C20" s="127" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="128"/>
+      <c r="E20" s="128"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27">
+        <v>4</v>
+      </c>
+      <c r="C21" s="176" t="s">
+        <v>139</v>
+      </c>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="178"/>
+      <c r="G21" s="89" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="30"/>
+      <c r="B22" s="29">
+        <v>5</v>
+      </c>
+      <c r="C22" s="221" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="223"/>
+      <c r="G22" s="98" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="25">
+        <v>2</v>
+      </c>
+      <c r="C23" s="127" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="26"/>
+      <c r="B24" s="27">
+        <v>3</v>
+      </c>
+      <c r="C24" s="127" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="129"/>
+      <c r="G24" s="89" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="26"/>
+      <c r="B25" s="27">
+        <v>4</v>
+      </c>
+      <c r="C25" s="176" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="177"/>
+      <c r="E25" s="177"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="30"/>
+      <c r="B26" s="29">
+        <v>5</v>
+      </c>
+      <c r="C26" s="136" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="98" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="25">
+        <v>2</v>
+      </c>
+      <c r="C27" s="127" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="128"/>
+      <c r="E27" s="128"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="31"/>
+      <c r="B28" s="27">
+        <v>3</v>
+      </c>
+      <c r="C28" s="127" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="128"/>
+      <c r="E28" s="128"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="89" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A29" s="31"/>
+      <c r="B29" s="27">
+        <v>4</v>
+      </c>
+      <c r="C29" s="215" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="216"/>
+      <c r="E29" s="216"/>
+      <c r="F29" s="217"/>
+      <c r="G29" s="89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="32"/>
+      <c r="B30" s="29">
+        <v>5</v>
+      </c>
+      <c r="C30" s="234" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="235"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="98" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="108"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
-    </row>
-    <row r="11" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="34">
+      <c r="B31" s="25">
         <v>2</v>
       </c>
-      <c r="C11" s="210" t="s">
-        <v>101</v>
-      </c>
-      <c r="D11" s="180"/>
-      <c r="E11" s="180"/>
-      <c r="F11" s="181"/>
-    </row>
-    <row r="12" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26">
+      <c r="C31" s="237" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" s="238"/>
+      <c r="E31" s="238"/>
+      <c r="F31" s="239"/>
+      <c r="G31" s="86" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27">
         <v>3</v>
       </c>
-      <c r="C12" s="195" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="196"/>
-      <c r="E12" s="196"/>
-      <c r="F12" s="197"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26">
+      <c r="C32" s="231" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="232"/>
+      <c r="E32" s="232"/>
+      <c r="F32" s="233"/>
+      <c r="G32" s="87" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27">
         <v>4</v>
       </c>
-      <c r="C13" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="133"/>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="64"/>
-      <c r="B14" s="55">
+      <c r="C33" s="228" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="229"/>
+      <c r="E33" s="229" t="s">
+        <v>147</v>
+      </c>
+      <c r="F33" s="230"/>
+      <c r="G33" s="87" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="38"/>
+      <c r="B34" s="29">
         <v>5</v>
       </c>
-      <c r="C14" s="211" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="212"/>
-      <c r="F14" s="213"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A15" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="24">
-        <v>2</v>
-      </c>
-      <c r="C15" s="115" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="117"/>
-    </row>
-    <row r="16" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26">
-        <v>3</v>
-      </c>
-      <c r="C16" s="131" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="133"/>
-    </row>
-    <row r="17" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="25"/>
-      <c r="B17" s="26">
-        <v>4</v>
-      </c>
-      <c r="C17" s="131" t="s">
-        <v>105</v>
-      </c>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="133"/>
-    </row>
-    <row r="18" spans="1:6" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="29"/>
-      <c r="B18" s="28">
-        <v>5</v>
-      </c>
-      <c r="C18" s="85" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="87"/>
-    </row>
-    <row r="19" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="24">
-        <v>2</v>
-      </c>
-      <c r="C19" s="207" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" s="208"/>
-      <c r="E19" s="208"/>
-      <c r="F19" s="209"/>
-    </row>
-    <row r="20" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26">
-        <v>3</v>
-      </c>
-      <c r="C20" s="91" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="92"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="93"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="25"/>
-      <c r="B21" s="26">
-        <v>4</v>
-      </c>
-      <c r="C21" s="131" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="133"/>
-    </row>
-    <row r="22" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="29"/>
-      <c r="B22" s="28">
-        <v>5</v>
-      </c>
-      <c r="C22" s="204" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="205"/>
-      <c r="E22" s="205"/>
-      <c r="F22" s="206"/>
-    </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="24">
-        <v>2</v>
-      </c>
-      <c r="C23" s="91" t="s">
-        <v>107</v>
-      </c>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="26">
-        <v>3</v>
-      </c>
-      <c r="C24" s="91" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="92"/>
-      <c r="E24" s="92"/>
-      <c r="F24" s="93"/>
-    </row>
-    <row r="25" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="26">
-        <v>4</v>
-      </c>
-      <c r="C25" s="131" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="133"/>
-    </row>
-    <row r="26" spans="1:6" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29"/>
-      <c r="B26" s="28">
-        <v>5</v>
-      </c>
-      <c r="C26" s="85" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="87"/>
-    </row>
-    <row r="27" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="24">
-        <v>2</v>
-      </c>
-      <c r="C27" s="91" t="s">
-        <v>111</v>
-      </c>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-      <c r="F27" s="93"/>
-    </row>
-    <row r="28" spans="1:6" ht="38.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="30"/>
-      <c r="B28" s="26">
-        <v>3</v>
-      </c>
-      <c r="C28" s="91" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="93"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A29" s="30"/>
-      <c r="B29" s="26">
-        <v>4</v>
-      </c>
-      <c r="C29" s="195" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="196"/>
-      <c r="E29" s="196"/>
-      <c r="F29" s="197"/>
-    </row>
-    <row r="30" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="31"/>
-      <c r="B30" s="28">
-        <v>5</v>
-      </c>
-      <c r="C30" s="198" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="199"/>
-      <c r="E30" s="199"/>
-      <c r="F30" s="200"/>
-    </row>
-    <row r="31" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="24">
-        <v>2</v>
-      </c>
-      <c r="C31" s="201" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="202"/>
-      <c r="E31" s="202"/>
-      <c r="F31" s="203"/>
-    </row>
-    <row r="32" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="35"/>
-      <c r="B32" s="26">
-        <v>3</v>
-      </c>
-      <c r="C32" s="192" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="193"/>
-      <c r="E32" s="193"/>
-      <c r="F32" s="194"/>
-    </row>
-    <row r="33" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="35"/>
-      <c r="B33" s="26">
-        <v>4</v>
-      </c>
-      <c r="C33" s="189" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="190"/>
-      <c r="E33" s="190" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="191"/>
-    </row>
-    <row r="34" spans="1:6" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="36"/>
-      <c r="B34" s="28">
-        <v>5</v>
-      </c>
-      <c r="C34" s="188" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" s="164"/>
-      <c r="E34" s="164" t="s">
-        <v>114</v>
-      </c>
-      <c r="F34" s="165"/>
-    </row>
-    <row r="35" spans="1:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C34" s="227" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="206"/>
+      <c r="E34" s="206" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="207"/>
+      <c r="G34" s="84" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="11.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
@@ -4090,7 +4593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B37" s="2" t="s">
         <v>17</v>
       </c>
@@ -4100,21 +4603,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="C33:D33"/>
@@ -4127,6 +4615,21 @@
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="C17:F17"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C19:F19"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C7"/>
